--- a/九龙-启德-维港．湾畔第1B期/维港．湾畔第1B期_销控明细表.xlsx
+++ b/九龙-启德-维港．湾畔第1B期/维港．湾畔第1B期_销控明细表.xlsx
@@ -1901,7 +1901,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -1963,7 +1963,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -3199,7 +3199,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
@@ -3813,7 +3813,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -4365,7 +4365,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -4427,7 +4427,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
@@ -4979,7 +4979,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="H64" s="5" t="n">
@@ -5041,7 +5041,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
@@ -5593,7 +5593,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
@@ -5655,7 +5655,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -6207,7 +6207,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="H83" s="5" t="n">
@@ -6821,7 +6821,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="H91" s="5" t="n">
@@ -6883,7 +6883,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="H92" s="5" t="n">
@@ -7435,7 +7435,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="H100" s="5" t="n">
@@ -7497,7 +7497,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="H101" s="5" t="n">
@@ -8049,7 +8049,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="H109" s="5" t="n">
@@ -8111,7 +8111,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="H110" s="5" t="n">
@@ -8173,7 +8173,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="H111" s="5" t="n">
@@ -8655,7 +8655,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="H118" s="5" t="n">
@@ -8717,7 +8717,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="H119" s="5" t="n">
@@ -8779,7 +8779,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="H120" s="5" t="n">
@@ -9261,7 +9261,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="H127" s="5" t="n">
@@ -9323,7 +9323,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="H128" s="5" t="n">
@@ -9385,7 +9385,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="H129" s="5" t="n">
@@ -9867,7 +9867,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="H136" s="5" t="n">
@@ -9929,7 +9929,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="H137" s="5" t="n">
@@ -9991,7 +9991,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H138" s="5" t="n">
@@ -10473,7 +10473,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="H145" s="5" t="n">
@@ -10535,7 +10535,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="H146" s="5" t="n">
@@ -11227,7 +11227,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="H156" s="5" t="n">
@@ -11709,7 +11709,7 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="H163" s="5" t="n">
@@ -11771,7 +11771,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="H164" s="5" t="n">
@@ -11833,7 +11833,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="H165" s="5" t="n">
@@ -12315,7 +12315,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="H172" s="5" t="n">
@@ -12377,7 +12377,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="H173" s="5" t="n">
@@ -12439,7 +12439,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="H174" s="5" t="n">
@@ -12921,7 +12921,7 @@
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="H181" s="5" t="n">
@@ -12983,7 +12983,7 @@
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="H182" s="5" t="n">
@@ -13045,7 +13045,7 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="H183" s="5" t="n">
@@ -13527,7 +13527,7 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="H190" s="5" t="n">
@@ -13589,7 +13589,7 @@
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="H191" s="5" t="n">
@@ -13651,7 +13651,7 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H192" s="5" t="n">
@@ -14133,7 +14133,7 @@
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="H199" s="5" t="n">
@@ -14195,7 +14195,7 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="H200" s="5" t="n">
@@ -14257,7 +14257,7 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H201" s="5" t="n">
@@ -14739,7 +14739,7 @@
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="H208" s="5" t="n">
@@ -14801,7 +14801,7 @@
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="H209" s="5" t="n">
@@ -14863,7 +14863,7 @@
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H210" s="5" t="n">
@@ -15345,7 +15345,7 @@
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="H217" s="5" t="n">
@@ -15407,7 +15407,7 @@
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="H218" s="5" t="n">
@@ -15469,7 +15469,7 @@
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H219" s="5" t="n">
@@ -15951,7 +15951,7 @@
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="H226" s="5" t="n">
@@ -16013,7 +16013,7 @@
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="H227" s="5" t="n">
@@ -16075,7 +16075,7 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H228" s="5" t="n">
@@ -16557,7 +16557,7 @@
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="H235" s="5" t="n">
@@ -16619,7 +16619,7 @@
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="H236" s="5" t="n">
@@ -16681,7 +16681,7 @@
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="H237" s="5" t="n">
@@ -17163,7 +17163,7 @@
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="H244" s="5" t="n">
@@ -17225,7 +17225,7 @@
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="H245" s="5" t="n">
@@ -17287,7 +17287,7 @@
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="H246" s="5" t="n">
@@ -17769,7 +17769,7 @@
       </c>
       <c r="G253" s="3" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="H253" s="5" t="n">
@@ -17831,7 +17831,7 @@
       </c>
       <c r="G254" s="3" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="H254" s="5" t="n">
@@ -17893,7 +17893,7 @@
       </c>
       <c r="G255" s="3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="H255" s="5" t="n">
@@ -18375,7 +18375,7 @@
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="H262" s="5" t="n">
@@ -18437,7 +18437,7 @@
       </c>
       <c r="G263" s="3" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="H263" s="5" t="n">
@@ -18911,7 +18911,7 @@
       </c>
       <c r="G270" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="H270" s="5" t="n">
@@ -19043,7 +19043,7 @@
       </c>
       <c r="G272" s="3" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="H272" s="5" t="n">
@@ -19517,7 +19517,7 @@
       </c>
       <c r="G279" s="3" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="H279" s="5" t="n">
@@ -19579,7 +19579,7 @@
       </c>
       <c r="G280" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H280" s="5" t="n">
@@ -19641,7 +19641,7 @@
       </c>
       <c r="G281" s="3" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="H281" s="5" t="n">
@@ -19703,7 +19703,7 @@
       </c>
       <c r="G282" s="3" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="H282" s="5" t="n">
@@ -20115,7 +20115,7 @@
       </c>
       <c r="G288" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H288" s="5" t="n">
@@ -20177,7 +20177,7 @@
       </c>
       <c r="G289" s="3" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="H289" s="5" t="n">
@@ -20239,7 +20239,7 @@
       </c>
       <c r="G290" s="3" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="H290" s="5" t="n">
@@ -20721,7 +20721,7 @@
       </c>
       <c r="G297" s="3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H297" s="5" t="n">
@@ -20783,7 +20783,7 @@
       </c>
       <c r="G298" s="3" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="H298" s="5" t="n">
@@ -20845,7 +20845,7 @@
       </c>
       <c r="G299" s="3" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="H299" s="5" t="n">
@@ -20907,7 +20907,7 @@
       </c>
       <c r="G300" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H300" s="5" t="n">
@@ -21319,7 +21319,7 @@
       </c>
       <c r="G306" s="3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H306" s="5" t="n">
@@ -21381,7 +21381,7 @@
       </c>
       <c r="G307" s="3" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="H307" s="5" t="n">
@@ -21443,7 +21443,7 @@
       </c>
       <c r="G308" s="3" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="H308" s="5" t="n">
@@ -21917,7 +21917,7 @@
       </c>
       <c r="G315" s="3" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H315" s="5" t="n">
@@ -21979,7 +21979,7 @@
       </c>
       <c r="G316" s="3" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="H316" s="5" t="n">
@@ -22041,7 +22041,7 @@
       </c>
       <c r="G317" s="3" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="H317" s="5" t="n">
@@ -22103,7 +22103,7 @@
       </c>
       <c r="G318" s="3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="H318" s="5" t="n">
@@ -22515,7 +22515,7 @@
       </c>
       <c r="G324" s="3" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="H324" s="5" t="n">
@@ -22577,7 +22577,7 @@
       </c>
       <c r="G325" s="3" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="H325" s="5" t="n">
@@ -22639,7 +22639,7 @@
       </c>
       <c r="G326" s="3" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="H326" s="5" t="n">
@@ -22701,7 +22701,7 @@
       </c>
       <c r="G327" s="3" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="H327" s="5" t="n">
@@ -23113,7 +23113,7 @@
       </c>
       <c r="G333" s="3" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="H333" s="5" t="n">
@@ -23175,7 +23175,7 @@
       </c>
       <c r="G334" s="3" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="H334" s="5" t="n">
@@ -23237,7 +23237,7 @@
       </c>
       <c r="G335" s="3" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="H335" s="5" t="n">
@@ -23711,7 +23711,7 @@
       </c>
       <c r="G342" s="3" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="H342" s="5" t="n">
@@ -23773,7 +23773,7 @@
       </c>
       <c r="G343" s="3" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="H343" s="5" t="n">
@@ -23835,7 +23835,7 @@
       </c>
       <c r="G344" s="3" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="H344" s="5" t="n">
@@ -23897,7 +23897,7 @@
       </c>
       <c r="G345" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H345" s="5" t="n">
@@ -24309,7 +24309,7 @@
       </c>
       <c r="G351" s="3" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="H351" s="5" t="n">
@@ -24371,7 +24371,7 @@
       </c>
       <c r="G352" s="3" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="H352" s="5" t="n">
@@ -24433,7 +24433,7 @@
       </c>
       <c r="G353" s="3" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="H353" s="5" t="n">
@@ -24495,7 +24495,7 @@
       </c>
       <c r="G354" s="3" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="H354" s="5" t="n">
@@ -24907,7 +24907,7 @@
       </c>
       <c r="G360" s="3" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="H360" s="5" t="n">
@@ -24969,7 +24969,7 @@
       </c>
       <c r="G361" s="3" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="H361" s="5" t="n">
@@ -25031,7 +25031,7 @@
       </c>
       <c r="G362" s="3" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="H362" s="5" t="n">
@@ -25093,7 +25093,7 @@
       </c>
       <c r="G363" s="3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="H363" s="5" t="n">
@@ -25505,7 +25505,7 @@
       </c>
       <c r="G369" s="3" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="H369" s="5" t="n">
@@ -25567,7 +25567,7 @@
       </c>
       <c r="G370" s="3" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="H370" s="5" t="n">
@@ -25629,7 +25629,7 @@
       </c>
       <c r="G371" s="3" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="H371" s="5" t="n">
@@ -25691,7 +25691,7 @@
       </c>
       <c r="G372" s="3" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="H372" s="5" t="n">
@@ -26103,7 +26103,7 @@
       </c>
       <c r="G378" s="3" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="H378" s="5" t="n">
@@ -26165,7 +26165,7 @@
       </c>
       <c r="G379" s="3" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="H379" s="5" t="n">
@@ -26227,7 +26227,7 @@
       </c>
       <c r="G380" s="3" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="H380" s="5" t="n">
@@ -26289,7 +26289,7 @@
       </c>
       <c r="G381" s="3" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="H381" s="5" t="n">
@@ -26701,7 +26701,7 @@
       </c>
       <c r="G387" s="3" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="H387" s="5" t="n">
@@ -26763,7 +26763,7 @@
       </c>
       <c r="G388" s="3" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="H388" s="5" t="n">
@@ -26825,7 +26825,7 @@
       </c>
       <c r="G389" s="3" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="H389" s="5" t="n">
@@ -26887,7 +26887,7 @@
       </c>
       <c r="G390" s="3" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="H390" s="5" t="n">
@@ -27299,7 +27299,7 @@
       </c>
       <c r="G396" s="3" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="H396" s="5" t="n">
@@ -27361,7 +27361,7 @@
       </c>
       <c r="G397" s="3" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="H397" s="5" t="n">
@@ -27423,7 +27423,7 @@
       </c>
       <c r="G398" s="3" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="H398" s="5" t="n">
@@ -27485,7 +27485,7 @@
       </c>
       <c r="G399" s="3" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="H399" s="5" t="n">
@@ -27897,7 +27897,7 @@
       </c>
       <c r="G405" s="3" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="H405" s="5" t="n">
@@ -27959,7 +27959,7 @@
       </c>
       <c r="G406" s="3" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="H406" s="5" t="n">
@@ -28021,7 +28021,7 @@
       </c>
       <c r="G407" s="3" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="H407" s="5" t="n">
@@ -28713,7 +28713,7 @@
       </c>
       <c r="G417" s="3" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="H417" s="5" t="n">
@@ -29125,7 +29125,7 @@
       </c>
       <c r="G423" s="3" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="H423" s="5" t="n">
@@ -29187,7 +29187,7 @@
       </c>
       <c r="G424" s="3" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="H424" s="5" t="n">
@@ -29249,7 +29249,7 @@
       </c>
       <c r="G425" s="3" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="H425" s="5" t="n">
@@ -29311,7 +29311,7 @@
       </c>
       <c r="G426" s="3" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="H426" s="5" t="n">
@@ -29723,7 +29723,7 @@
       </c>
       <c r="G432" s="3" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="H432" s="5" t="n">
@@ -29785,7 +29785,7 @@
       </c>
       <c r="G433" s="3" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="H433" s="5" t="n">
@@ -29847,7 +29847,7 @@
       </c>
       <c r="G434" s="3" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="H434" s="5" t="n">
@@ -29909,7 +29909,7 @@
       </c>
       <c r="G435" s="3" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="H435" s="5" t="n">
@@ -30321,7 +30321,7 @@
       </c>
       <c r="G441" s="3" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="H441" s="5" t="n">
@@ -30383,7 +30383,7 @@
       </c>
       <c r="G442" s="3" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="H442" s="5" t="n">
@@ -30445,7 +30445,7 @@
       </c>
       <c r="G443" s="3" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="H443" s="5" t="n">
@@ -30507,7 +30507,7 @@
       </c>
       <c r="G444" s="3" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="H444" s="5" t="n">
@@ -30919,7 +30919,7 @@
       </c>
       <c r="G450" s="3" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="H450" s="5" t="n">
@@ -30981,7 +30981,7 @@
       </c>
       <c r="G451" s="3" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="H451" s="5" t="n">
@@ -31043,7 +31043,7 @@
       </c>
       <c r="G452" s="3" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="H452" s="5" t="n">
@@ -31105,7 +31105,7 @@
       </c>
       <c r="G453" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="H453" s="5" t="n">
@@ -31517,7 +31517,7 @@
       </c>
       <c r="G459" s="3" t="inlineStr">
         <is>
-          <t>2026-01-11</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="H459" s="5" t="n">
@@ -31579,7 +31579,7 @@
       </c>
       <c r="G460" s="3" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="H460" s="5" t="n">
@@ -31641,7 +31641,7 @@
       </c>
       <c r="G461" s="3" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="H461" s="5" t="n">
@@ -31703,7 +31703,7 @@
       </c>
       <c r="G462" s="3" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="H462" s="5" t="n">
@@ -32115,7 +32115,7 @@
       </c>
       <c r="G468" s="3" t="inlineStr">
         <is>
-          <t>2026-01-11</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="H468" s="5" t="n">
@@ -32177,7 +32177,7 @@
       </c>
       <c r="G469" s="3" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="H469" s="5" t="n">
@@ -32239,7 +32239,7 @@
       </c>
       <c r="G470" s="3" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="H470" s="5" t="n">
@@ -32301,7 +32301,7 @@
       </c>
       <c r="G471" s="3" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="H471" s="5" t="n">
@@ -32713,7 +32713,7 @@
       </c>
       <c r="G477" s="3" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="H477" s="5" t="n">
@@ -32775,7 +32775,7 @@
       </c>
       <c r="G478" s="3" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="H478" s="5" t="n">
@@ -32837,7 +32837,7 @@
       </c>
       <c r="G479" s="3" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="H479" s="5" t="n">
@@ -32899,7 +32899,7 @@
       </c>
       <c r="G480" s="3" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="H480" s="5" t="n">
@@ -33311,7 +33311,7 @@
       </c>
       <c r="G486" s="3" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="H486" s="5" t="n">
@@ -33373,7 +33373,7 @@
       </c>
       <c r="G487" s="3" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="H487" s="5" t="n">
@@ -33435,7 +33435,7 @@
       </c>
       <c r="G488" s="3" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="H488" s="5" t="n">
@@ -33497,7 +33497,7 @@
       </c>
       <c r="G489" s="3" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="H489" s="5" t="n">
@@ -33909,7 +33909,7 @@
       </c>
       <c r="G495" s="3" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="H495" s="5" t="n">
@@ -33971,7 +33971,7 @@
       </c>
       <c r="G496" s="3" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="H496" s="5" t="n">
@@ -34033,7 +34033,7 @@
       </c>
       <c r="G497" s="3" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="H497" s="5" t="n">
@@ -34095,7 +34095,7 @@
       </c>
       <c r="G498" s="3" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="H498" s="5" t="n">
@@ -34437,7 +34437,7 @@
       </c>
       <c r="G503" s="3" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="H503" s="5" t="n">
@@ -34499,7 +34499,7 @@
       </c>
       <c r="G504" s="3" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="H504" s="5" t="n">
@@ -34561,7 +34561,7 @@
       </c>
       <c r="G505" s="3" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="H505" s="5" t="n">
@@ -34623,7 +34623,7 @@
       </c>
       <c r="G506" s="3" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="H506" s="5" t="n">
@@ -34825,7 +34825,7 @@
       </c>
       <c r="G509" s="3" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="H509" s="5" t="n">
@@ -34887,7 +34887,7 @@
       </c>
       <c r="G510" s="3" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="H510" s="5" t="n">
@@ -35089,7 +35089,7 @@
       </c>
       <c r="G513" s="3" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="H513" s="5" t="n">
@@ -35363,7 +35363,7 @@
           <t>A | 560呎 (2房)
 $1921万
 $34,307/呎
-(26年-06月-16日)</t>
+(26年-06月-17日)</t>
         </is>
       </c>
       <c r="C6" s="22" t="inlineStr">
@@ -35371,7 +35371,7 @@
           <t>B | 516呎 (2房)
 $1742万
 $33,756/呎
-(26年-06月-10日)</t>
+(26年-06月-11日)</t>
         </is>
       </c>
       <c r="D6" s="21" t="inlineStr">
@@ -35450,7 +35450,7 @@
           <t>B | 516呎 (2房)
 $1692万
 $32,791/呎
-(26年-06月-10日)</t>
+(26年-06月-11日)</t>
         </is>
       </c>
       <c r="D7" s="21" t="inlineStr">
@@ -35521,7 +35521,7 @@
           <t>A | 560呎 (2房)
 $1848万
 $32,993/呎
-(26年-05月-31日)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -35529,7 +35529,7 @@
           <t>B | 516呎 (2房)
 $1675万
 $32,467/呎
-(26年-06月-23日)</t>
+(26年-06月-24日)</t>
         </is>
       </c>
       <c r="D8" s="21" t="inlineStr">
@@ -35600,7 +35600,7 @@
           <t>A | 560呎 (2房)
 $1794万
 $32,030/呎
-(26年-04月-19日)</t>
+(26年-04月-20日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -35608,7 +35608,7 @@
           <t>B | 516呎 (2房)
 $1627万
 $31,527/呎
-(26年-04月-19日)</t>
+(26年-04月-20日)</t>
         </is>
       </c>
       <c r="D9" s="21" t="inlineStr">
@@ -35679,7 +35679,7 @@
           <t>A | 560呎 (2房)
 $1776万
 $31,714/呎
-(26年-05月-14日)</t>
+(26年-05月-15日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -35687,7 +35687,7 @@
           <t>B | 516呎 (2房)
 $1611万
 $31,215/呎
-(26年-05月-07日)</t>
+(26年-05月-08日)</t>
         </is>
       </c>
       <c r="D10" s="21" t="inlineStr">
@@ -35758,7 +35758,7 @@
           <t>A | 560呎 (2房)
 $1758万
 $31,400/呎
-(26年-04月-09日)</t>
+(26年-04月-10日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -35766,7 +35766,7 @@
           <t>B | 516呎 (2房)
 $1595万
 $30,907/呎
-(26年-03月-24日)</t>
+(26年-03月-25日)</t>
         </is>
       </c>
       <c r="D11" s="21" t="inlineStr">
@@ -35837,7 +35837,7 @@
           <t>A | 560呎 (2房)
 $1743万
 $31,130/呎
-(26年-02月-10日)</t>
+(26年-02月-11日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -35845,7 +35845,7 @@
           <t>B | 516呎 (2房)
 $1548万
 $30,000/呎
-(26年-02月-04日)</t>
+(26年-02月-05日)</t>
         </is>
       </c>
       <c r="D12" s="21" t="inlineStr">
@@ -35916,7 +35916,7 @@
           <t>A | 560呎 (2房)
 $1715万
 $30,627/呎
-(26年-02月-08日)</t>
+(26年-02月-09日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -35924,7 +35924,7 @@
           <t>B | 516呎 (2房)
 $1540万
 $29,851/呎
-(26年-02月-05日)</t>
+(26年-02月-06日)</t>
         </is>
       </c>
       <c r="D13" s="21" t="inlineStr">
@@ -35995,7 +35995,7 @@
           <t>A | 560呎 (2房)
 $1707万
 $30,475/呎
-(25年-09月-09日)</t>
+(25年-09月-10日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -36003,7 +36003,7 @@
           <t>B | 516呎 (2房)
 $1533万
 $29,702/呎
-(25年-09月-16日)</t>
+(25年-09月-17日)</t>
         </is>
       </c>
       <c r="D14" s="21" t="inlineStr">
@@ -36074,7 +36074,7 @@
           <t>A | 560呎 (2房)
 $1715万
 $30,627/呎
-(26年-03月-24日)</t>
+(26年-03月-25日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -36082,7 +36082,7 @@
           <t>B | 516呎 (2房)
 $1525万
 $29,554/呎
-(26年-02月-23日)</t>
+(26年-02月-24日)</t>
         </is>
       </c>
       <c r="D15" s="21" t="inlineStr">
@@ -36153,7 +36153,7 @@
           <t>A | 560呎 (2房)
 $1707万
 $30,475/呎
-(26年-03月-29日)</t>
+(26年-03月-30日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -36161,7 +36161,7 @@
           <t>B | 516呎 (2房)
 $1517万
 $29,407/呎
-(25年-12月-08日)</t>
+(25年-12月-09日)</t>
         </is>
       </c>
       <c r="D16" s="21" t="inlineStr">
@@ -36232,7 +36232,7 @@
           <t>A | 560呎 (2房)
 $1681万
 $30,023/呎
-(25年-09月-10日)</t>
+(25年-09月-11日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -36240,7 +36240,7 @@
           <t>B | 516呎 (2房)
 $1510万
 $29,260/呎
-(25年-12月-22日)</t>
+(25年-12月-23日)</t>
         </is>
       </c>
       <c r="D17" s="21" t="inlineStr">
@@ -36296,7 +36296,7 @@
           <t>J | 559呎 (2房)
 $1832万
 $32,771/呎
-(26年-06月-10日)</t>
+(26年-06月-11日)</t>
         </is>
       </c>
     </row>
@@ -36311,7 +36311,7 @@
           <t>A | 560呎 (2房)
 $1673万
 $29,873/呎
-(25年-12月-03日)</t>
+(25年-12月-04日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -36319,7 +36319,7 @@
           <t>B | 516呎 (2房)
 $1502万
 $29,114/呎
-(25年-11月-26日)</t>
+(25年-11月-27日)</t>
         </is>
       </c>
       <c r="D18" s="21" t="inlineStr">
@@ -36375,7 +36375,7 @@
           <t>J | 559呎 (2房)
 $1823万
 $32,610/呎
-(26年-05月-17日)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
     </row>
@@ -36390,7 +36390,7 @@
           <t>A | 560呎 (2房)
 $1664万
 $29,723/呎
-(26年-01月-21日)</t>
+(26年-01月-22日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -36398,7 +36398,7 @@
           <t>B | 516呎 (2房)
 $1495万
 $28,969/呎
-(25年-11月-18日)</t>
+(25年-11月-19日)</t>
         </is>
       </c>
       <c r="D19" s="21" t="inlineStr">
@@ -36454,7 +36454,7 @@
           <t>J | 559呎 (2房)
 $1780万
 $31,844/呎
-(26年-05月-14日)</t>
+(26年-05月-15日)</t>
         </is>
       </c>
     </row>
@@ -36469,7 +36469,7 @@
           <t>A | 560呎 (2房)
 $1694万
 $30,246/呎
-(25年-10月-23日)</t>
+(25年-10月-24日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -36477,7 +36477,7 @@
           <t>B | 516呎 (2房)
 $1487万
 $28,826/呎
-(25年-11月-07日)</t>
+(25年-11月-08日)</t>
         </is>
       </c>
       <c r="D20" s="21" t="inlineStr">
@@ -36533,7 +36533,7 @@
           <t>J | 559呎 (2房)
 $1805万
 $32,283/呎
-(26年-06月-02日)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
     </row>
@@ -36627,7 +36627,7 @@
           <t>A | 560呎 (2房)
 $1631万
 $29,132/呎
-(25年-09月-09日)</t>
+(25年-09月-10日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -36635,7 +36635,7 @@
           <t>B | 516呎 (2房)
 $1465万
 $28,393/呎
-(25年-09月-04日)</t>
+(25年-09月-05日)</t>
         </is>
       </c>
       <c r="D22" s="21" t="inlineStr">
@@ -36691,7 +36691,7 @@
           <t>J | 559呎 (2房)
 $1734万
 $31,018/呎
-(26年-05月-04日)</t>
+(26年-05月-05日)</t>
         </is>
       </c>
     </row>
@@ -36706,7 +36706,7 @@
           <t>A | 560呎 (2房)
 $1623万
 $28,988/呎
-(26年-01月-19日)</t>
+(26年-01月-20日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -36714,7 +36714,7 @@
           <t>B | 516呎 (2房)
 $1458万
 $28,252/呎
-(25年-11月-03日)</t>
+(25年-11月-04日)</t>
         </is>
       </c>
       <c r="D23" s="21" t="inlineStr">
@@ -36770,7 +36770,7 @@
           <t>J | 559呎 (2房)
 $1759万
 $31,460/呎
-(26年-04月-26日)</t>
+(26年-04月-27日)</t>
         </is>
       </c>
     </row>
@@ -36785,7 +36785,7 @@
           <t>A | 560呎 (2房)
 $1615万
 $28,843/呎
-(25年-12月-07日)</t>
+(25年-12月-08日)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -36793,7 +36793,7 @@
           <t>B | 516呎 (2房)
 $1450万
 $28,110/呎
-(25年-09月-08日)</t>
+(25年-09月-09日)</t>
         </is>
       </c>
       <c r="D24" s="21" t="inlineStr">
@@ -36849,7 +36849,7 @@
           <t>J | 559呎 (2房)
 $1711万
 $30,608/呎
-(26年-04月-26日)</t>
+(26年-04月-27日)</t>
         </is>
       </c>
     </row>
@@ -36864,7 +36864,7 @@
           <t>A | 560呎 (2房)
 $1607万
 $28,698/呎
-(25年-12月-07日)</t>
+(25年-12月-08日)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -36872,7 +36872,7 @@
           <t>B | 516呎 (2房)
 $1443万
 $27,969/呎
-(25年-09月-17日)</t>
+(25年-09月-18日)</t>
         </is>
       </c>
       <c r="D25" s="21" t="inlineStr">
@@ -36928,7 +36928,7 @@
           <t>J | 559呎 (2房)
 $1758万
 $31,444/呎
-(26年-04月-29日)</t>
+(26年-04月-30日)</t>
         </is>
       </c>
     </row>
@@ -36943,7 +36943,7 @@
           <t>A | 560呎 (2房)
 $1599万
 $28,555/呎
-(26年-01月-21日)</t>
+(26年-01月-22日)</t>
         </is>
       </c>
       <c r="C26" s="22" t="inlineStr">
@@ -36951,7 +36951,7 @@
           <t>B | 516呎 (2房)
 $1436万
 $27,829/呎
-(25年-11月-05日)</t>
+(25年-11月-06日)</t>
         </is>
       </c>
       <c r="D26" s="21" t="inlineStr">
@@ -37007,7 +37007,7 @@
           <t>J | 559呎 (2房)
 $1710万
 $30,592/呎
-(26年-05月-20日)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
     </row>
@@ -37022,7 +37022,7 @@
           <t>A | 560呎 (2房)
 $1591万
 $28,412/呎
-(26年-01月-19日)</t>
+(26年-01月-20日)</t>
         </is>
       </c>
       <c r="C27" s="22" t="inlineStr">
@@ -37030,7 +37030,7 @@
           <t>B | 516呎 (2房)
 $1429万
 $27,692/呎
-(25年-09月-08日)</t>
+(25年-09月-09日)</t>
         </is>
       </c>
       <c r="D27" s="21" t="inlineStr">
@@ -37086,7 +37086,7 @@
           <t>J | 559呎 (2房)
 $1702万
 $30,440/呎
-(26年-05月-05日)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
     </row>
@@ -37101,7 +37101,7 @@
           <t>A | 560呎 (2房)
 $1583万
 $28,270/呎
-(25年-11月-20日)</t>
+(25年-11月-21日)</t>
         </is>
       </c>
       <c r="C28" s="22" t="inlineStr">
@@ -37109,7 +37109,7 @@
           <t>B | 516呎 (2房)
 $1422万
 $27,552/呎
-(25年-10月-12日)</t>
+(25年-10月-13日)</t>
         </is>
       </c>
       <c r="D28" s="21" t="inlineStr">
@@ -37165,7 +37165,7 @@
           <t>J | 559呎 (2房)
 $1693万
 $30,288/呎
-(26年-04月-20日)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
     </row>
@@ -37180,7 +37180,7 @@
           <t>A | 560呎 (2房)
 $1559万
 $27,846/呎
-(25年-09月-14日)</t>
+(25年-09月-15日)</t>
         </is>
       </c>
       <c r="C29" s="22" t="inlineStr">
@@ -37188,7 +37188,7 @@
           <t>B | 516呎 (2房)
 $1400万
 $27,140/呎
-(25年-09月-01日)</t>
+(25年-09月-02日)</t>
         </is>
       </c>
       <c r="D29" s="21" t="inlineStr">
@@ -37244,7 +37244,7 @@
           <t>J | 559呎 (2房)
 $1652万
 $29,551/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
     </row>
@@ -37259,7 +37259,7 @@
           <t>A | 560呎 (2房)
 $1579万
 $28,195/呎
-(25年-09月-08日)</t>
+(25年-09月-09日)</t>
         </is>
       </c>
       <c r="C30" s="22" t="inlineStr">
@@ -37267,7 +37267,7 @@
           <t>B | 516呎 (2房)
 $1386万
 $26,868/呎
-(25年-09月-01日)</t>
+(25年-09月-02日)</t>
         </is>
       </c>
       <c r="D30" s="21" t="inlineStr">
@@ -37323,7 +37323,7 @@
           <t>J | 559呎 (2房)
 $1620万
 $28,977/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
     </row>
@@ -37338,7 +37338,7 @@
           <t>A | 560呎 (2房)
 $1528万
 $27,291/呎
-(25年-08月-14日)</t>
+(25年-08月-15日)</t>
         </is>
       </c>
       <c r="C31" s="22" t="inlineStr">
@@ -37346,7 +37346,7 @@
           <t>B | 516呎 (2房)
 $1372万
 $26,599/呎
-(25年-09月-14日)</t>
+(25年-09月-15日)</t>
         </is>
       </c>
       <c r="D31" s="21" t="inlineStr">
@@ -37402,7 +37402,7 @@
           <t>J | 559呎 (2房)
 $1619万
 $28,962/呎
-(26年-04月-29日)</t>
+(26年-04月-30日)</t>
         </is>
       </c>
     </row>
@@ -37417,7 +37417,7 @@
           <t>A | 560呎 (2房)
 $1540万
 $27,493/呎
-(25年-12月-15日)</t>
+(25年-12月-16日)</t>
         </is>
       </c>
       <c r="C32" s="22" t="inlineStr">
@@ -37425,7 +37425,7 @@
           <t>B | 516呎 (2房)
 $1352万
 $26,200/呎
-(25年-09月-01日)</t>
+(25年-09月-02日)</t>
         </is>
       </c>
       <c r="D32" s="21" t="inlineStr">
@@ -37481,7 +37481,7 @@
           <t>J | 559呎 (2房)
 $1580万
 $28,258/呎
-(26年-04月-14日)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
     </row>
@@ -37496,7 +37496,7 @@
           <t>A | 560呎 (2房)
 $1483万
 $26,488/呎
-(25年-12月-04日)</t>
+(25年-12月-05日)</t>
         </is>
       </c>
       <c r="C33" s="22" t="inlineStr">
@@ -37504,7 +37504,7 @@
           <t>B | 516呎 (2房)
 $1333万
 $25,828/呎
-(25年-10月-12日)</t>
+(25年-10月-13日)</t>
         </is>
       </c>
       <c r="D33" s="21" t="inlineStr">
@@ -37560,7 +37560,7 @@
           <t>J | 559呎 (2房)
 $1586万
 $28,369/呎
-(26年-05月-18日)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
     </row>
@@ -37728,7 +37728,7 @@
           <t>A | 670呎 (3房)
 $2424万
 $36,187/呎
-(26年-04月-12日)</t>
+(26年-04月-13日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr">
@@ -37744,7 +37744,7 @@
           <t>C | 568呎 (3房)
 $2117万
 $37,276/呎
-(26年-06月-11日)</t>
+(26年-06月-12日)</t>
         </is>
       </c>
       <c r="E5" s="21" t="inlineStr">
@@ -37807,7 +37807,7 @@
           <t>A | 670呎 (3房)
 $2320万
 $34,634/呎
-(26年-03月-02日)</t>
+(26年-03月-03日)</t>
         </is>
       </c>
       <c r="C6" s="22" t="inlineStr">
@@ -37815,7 +37815,7 @@
           <t>B | 579呎 (2房)
 $2047万
 $35,361/呎
-(26年-05月-20日)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="D6" s="22" t="inlineStr">
@@ -37823,7 +37823,7 @@
           <t>C | 568呎 (3房)
 $1993万
 $35,086/呎
-(26年-03月-02日)</t>
+(26年-03月-03日)</t>
         </is>
       </c>
       <c r="E6" s="21" t="inlineStr">
@@ -37886,7 +37886,7 @@
           <t>A | 670呎 (3房)
 $2298万
 $34,291/呎
-(26年-02月-12日)</t>
+(26年-02月-13日)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -37894,7 +37894,7 @@
           <t>B | 579呎 (2房)
 $1956万
 $33,777/呎
-(26年-01月-19日)</t>
+(26年-01月-20日)</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">
@@ -37902,7 +37902,7 @@
           <t>C | 568呎 (3房)
 $2050万
 $36,088/呎
-(26年-05月-21日)</t>
+(26年-05月-22日)</t>
         </is>
       </c>
       <c r="E7" s="21" t="inlineStr">
@@ -37950,7 +37950,7 @@
           <t>J | 549呎 (2房)
 $1825万
 $33,242/呎
-(26年-03月-09日)</t>
+(26年-03月-10日)</t>
         </is>
       </c>
     </row>
@@ -37965,7 +37965,7 @@
           <t>A | 670呎 (3房)
 $2275万
 $33,952/呎
-(26年-02月-03日)</t>
+(26年-02月-04日)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -37973,7 +37973,7 @@
           <t>B | 579呎 (2房)
 $1931万
 $33,356/呎
-(26年-02月-08日)</t>
+(26年-02月-09日)</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
@@ -37981,7 +37981,7 @@
           <t>C | 568呎 (3房)
 $2086万
 $36,732/呎
-(26年-07月-06日)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
       <c r="E8" s="21" t="inlineStr">
@@ -38044,7 +38044,7 @@
           <t>A | 670呎 (3房)
 $2252万
 $33,613/呎
-(26年-01月-08日)</t>
+(26年-01月-09日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -38052,7 +38052,7 @@
           <t>B | 579呎 (2房)
 $1912万
 $33,026/呎
-(26年-02月-03日)</t>
+(26年-02月-04日)</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
@@ -38060,7 +38060,7 @@
           <t>C | 568呎 (3房)
 $1972万
 $34,715/呎
-(26年-05月-31日)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="E9" s="21" t="inlineStr">
@@ -38108,7 +38108,7 @@
           <t>J | 549呎 (2房)
 $1878万
 $34,217/呎
-(26年-06月-02日)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
     </row>
@@ -38123,7 +38123,7 @@
           <t>A | 670呎 (3房)
 $2230万
 $33,282/呎
-(25年-12月-23日)</t>
+(25年-12月-24日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -38131,7 +38131,7 @@
           <t>B | 579呎 (2房)
 $1968万
 $33,981/呎
-(26年-05月-17日)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -38139,7 +38139,7 @@
           <t>C | 568呎 (3房)
 $1952万
 $34,371/呎
-(26年-05月-11日)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="E10" s="21" t="inlineStr">
@@ -38202,7 +38202,7 @@
           <t>A | 670呎 (3房)
 $2186万
 $32,630/呎
-(25年-12月-04日)</t>
+(25年-12月-05日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -38210,7 +38210,7 @@
           <t>B | 579呎 (2房)
 $1948万
 $33,644/呎
-(26年-05月-14日)</t>
+(26年-05月-15日)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -38218,7 +38218,7 @@
           <t>C | 568呎 (3房)
 $1915万
 $33,708/呎
-(26年-04月-09日)</t>
+(26年-04月-10日)</t>
         </is>
       </c>
       <c r="E11" s="21" t="inlineStr">
@@ -38266,7 +38266,7 @@
           <t>J | 549呎 (2房)
 $1789万
 $32,583/呎
-(26年-04月-14日)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
     </row>
@@ -38281,7 +38281,7 @@
           <t>A | 669呎 (3房)
 $2143万
 $32,033/呎
-(25年-10月-02日)</t>
+(25年-10月-03日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -38289,7 +38289,7 @@
           <t>B | 579呎 (2房)
 $1856万
 $32,054/呎
-(26年-02月-12日)</t>
+(26年-02月-13日)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -38297,7 +38297,7 @@
           <t>C | 568呎 (3房)
 $1859万
 $32,732/呎
-(26年-01月-21日)</t>
+(26年-01月-22日)</t>
         </is>
       </c>
       <c r="E12" s="21" t="inlineStr">
@@ -38345,7 +38345,7 @@
           <t>J | 549呎 (2房)
 $1791万
 $32,630/呎
-(26年-04月-19日)</t>
+(26年-04月-20日)</t>
         </is>
       </c>
     </row>
@@ -38360,7 +38360,7 @@
           <t>A | 669呎 (3房)
 $2132万
 $31,874/呎
-(25年-09月-11日)</t>
+(25年-09月-12日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -38368,7 +38368,7 @@
           <t>B | 579呎 (2房)
 $1831万
 $31,623/呎
-(26年-01月-05日)</t>
+(26年-01月-06日)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -38376,7 +38376,7 @@
           <t>C | 568呎 (3房)
 $1814万
 $31,930/呎
-(26年-01月-15日)</t>
+(26年-01月-16日)</t>
         </is>
       </c>
       <c r="E13" s="21" t="inlineStr">
@@ -38439,7 +38439,7 @@
           <t>A | 670呎 (3房)
 $2192万
 $32,713/呎
-(25年-10月-19日)</t>
+(25年-10月-20日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -38447,7 +38447,7 @@
           <t>B | 579呎 (2房)
 $1802万
 $31,114/呎
-(26年-01月-06日)</t>
+(26年-01月-07日)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -38455,7 +38455,7 @@
           <t>C | 568呎 (3房)
 $1841万
 $32,407/呎
-(26年-02月-12日)</t>
+(26年-02月-13日)</t>
         </is>
       </c>
       <c r="E14" s="21" t="inlineStr">
@@ -38503,7 +38503,7 @@
           <t>J | 549呎 (2房)
 $1805万
 $32,880/呎
-(26年-05月-12日)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
     </row>
@@ -38518,7 +38518,7 @@
           <t>A | 670呎 (3房)
 $2174万
 $32,455/呎
-(25年-10月-21日)</t>
+(25年-10月-22日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -38526,7 +38526,7 @@
           <t>B | 579呎 (2房)
 $1792万
 $30,959/呎
-(25年-09月-25日)</t>
+(25年-09月-26日)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -38534,7 +38534,7 @@
           <t>C | 568呎 (3房)
 $1868万
 $32,879/呎
-(26年-03月-15日)</t>
+(26年-03月-16日)</t>
         </is>
       </c>
       <c r="E15" s="21" t="inlineStr">
@@ -38582,7 +38582,7 @@
           <t>J | 549呎 (2房)
 $1745万
 $31,783/呎
-(26年-04月-29日)</t>
+(26年-04月-30日)</t>
         </is>
       </c>
     </row>
@@ -38597,7 +38597,7 @@
           <t>A | 669呎 (3房)
 $2101万
 $31,401/呎
-(25年-10月-02日)</t>
+(25年-10月-03日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -38605,7 +38605,7 @@
           <t>B | 579呎 (2房)
 $1784万
 $30,805/呎
-(25年-09月-11日)</t>
+(25年-09月-12日)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -38613,7 +38613,7 @@
           <t>C | 568呎 (3房)
 $1822万
 $32,086/呎
-(26年-02月-09日)</t>
+(26年-02月-10日)</t>
         </is>
       </c>
       <c r="E16" s="21" t="inlineStr">
@@ -38661,7 +38661,7 @@
           <t>J | 549呎 (2房)
 $1736万
 $31,625/呎
-(26年-04月-26日)</t>
+(26年-04月-27日)</t>
         </is>
       </c>
     </row>
@@ -38676,7 +38676,7 @@
           <t>A | 669呎 (3房)
 $2090万
 $31,245/呎
-(25年-09月-10日)</t>
+(25年-09月-11日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -38684,7 +38684,7 @@
           <t>B | 579呎 (2房)
 $1775万
 $30,651/呎
-(25年-10月-12日)</t>
+(25年-10月-13日)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -38692,7 +38692,7 @@
           <t>C | 569呎 (3房)
 $1778万
 $31,244/呎
-(25年-09月-10日)</t>
+(25年-09月-11日)</t>
         </is>
       </c>
       <c r="E17" s="21" t="inlineStr">
@@ -38740,7 +38740,7 @@
           <t>J | 549呎 (2房)
 $1728万
 $31,466/呎
-(26年-04月-13日)</t>
+(26年-04月-14日)</t>
         </is>
       </c>
     </row>
@@ -38755,7 +38755,7 @@
           <t>A | 669呎 (3房)
 $2104万
 $31,444/呎
-(25年-09月-15日)</t>
+(25年-09月-16日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -38763,7 +38763,7 @@
           <t>B | 579呎 (2房)
 $1766万
 $30,499/呎
-(25年-09月-10日)</t>
+(25年-09月-11日)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -38771,7 +38771,7 @@
           <t>C | 568呎 (3房)
 $1769万
 $31,144/呎
-(25年-12月-10日)</t>
+(25年-12月-11日)</t>
         </is>
       </c>
       <c r="E18" s="21" t="inlineStr">
@@ -38819,7 +38819,7 @@
           <t>J | 549呎 (2房)
 $1719万
 $31,311/呎
-(26年-04月-01日)</t>
+(26年-04月-02日)</t>
         </is>
       </c>
     </row>
@@ -38834,7 +38834,7 @@
           <t>A | 669呎 (3房)
 $2070万
 $30,934/呎
-(25年-09月-28日)</t>
+(25年-09月-29日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -38842,7 +38842,7 @@
           <t>B | 579呎 (2房)
 $1757万
 $30,347/呎
-(25年-11月-08日)</t>
+(25年-11月-09日)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -38850,7 +38850,7 @@
           <t>C | 568呎 (3房)
 $1760万
 $30,988/呎
-(25年-12月-18日)</t>
+(25年-12月-19日)</t>
         </is>
       </c>
       <c r="E19" s="21" t="inlineStr">
@@ -38898,7 +38898,7 @@
           <t>J | 549呎 (2房)
 $1694万
 $30,849/呎
-(26年-03月-10日)</t>
+(26年-03月-11日)</t>
         </is>
       </c>
     </row>
@@ -38913,7 +38913,7 @@
           <t>A | 670呎 (3房)
 $2082万
 $31,082/呎
-(25年-09月-18日)</t>
+(25年-09月-19日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -38921,7 +38921,7 @@
           <t>B | 579呎 (2房)
 $1748万
 $30,195/呎
-(25年-10月-02日)</t>
+(25年-10月-03日)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -38929,7 +38929,7 @@
           <t>C | 568呎 (3房)
 $1791万
 $31,533/呎
-(25年-09月-10日)</t>
+(25年-09月-11日)</t>
         </is>
       </c>
       <c r="E20" s="21" t="inlineStr">
@@ -38977,7 +38977,7 @@
           <t>J | 549呎 (2房)
 $1685万
 $30,694/呎
-(26年-03月-22日)</t>
+(26年-03月-23日)</t>
         </is>
       </c>
     </row>
@@ -39071,7 +39071,7 @@
           <t>A | 669呎 (3房)
 $2028万
 $30,318/呎
-(25年-09月-10日)</t>
+(25年-09月-11日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -39079,7 +39079,7 @@
           <t>B | 579呎 (2房)
 $1722万
 $29,743/呎
-(25年-09月-11日)</t>
+(25年-09月-12日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -39087,7 +39087,7 @@
           <t>C | 569呎 (3房)
 $1725万
 $30,318/呎
-(25年-09月-10日)</t>
+(25年-09月-11日)</t>
         </is>
       </c>
       <c r="E22" s="21" t="inlineStr">
@@ -39135,7 +39135,7 @@
           <t>J | 549呎 (2房)
 $1676万
 $30,534/呎
-(26年-04月-01日)</t>
+(26年-04月-02日)</t>
         </is>
       </c>
     </row>
@@ -39150,7 +39150,7 @@
           <t>A | 669呎 (3房)
 $2018万
 $30,167/呎
-(25年-09月-16日)</t>
+(25年-09月-17日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -39158,7 +39158,7 @@
           <t>B | 579呎 (2房)
 $1714万
 $29,594/呎
-(25年-09月-24日)</t>
+(25年-09月-25日)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -39166,7 +39166,7 @@
           <t>C | 568呎 (3房)
 $1716万
 $30,220/呎
-(25年-11月-24日)</t>
+(25年-11月-25日)</t>
         </is>
       </c>
       <c r="E23" s="21" t="inlineStr">
@@ -39214,7 +39214,7 @@
           <t>J | 549呎 (2房)
 $1668万
 $30,383/呎
-(26年-03月-26日)</t>
+(26年-03月-27日)</t>
         </is>
       </c>
     </row>
@@ -39229,7 +39229,7 @@
           <t>A | 669呎 (3房)
 $2008万
 $30,016/呎
-(25年-09月-10日)</t>
+(25年-09月-11日)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -39237,7 +39237,7 @@
           <t>B | 579呎 (2房)
 $1724万
 $29,781/呎
-(25年-09月-15日)</t>
+(25年-09月-16日)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -39245,7 +39245,7 @@
           <t>C | 568呎 (3房)
 $1708万
 $30,069/呎
-(26年-01月-18日)</t>
+(26年-01月-19日)</t>
         </is>
       </c>
       <c r="E24" s="21" t="inlineStr">
@@ -39293,7 +39293,7 @@
           <t>J | 549呎 (2房)
 $1681万
 $30,614/呎
-(26年-03月-18日)</t>
+(26年-03月-19日)</t>
         </is>
       </c>
     </row>
@@ -39308,7 +39308,7 @@
           <t>A | 669呎 (3房)
 $1998万
 $29,867/呎
-(25年-10月-02日)</t>
+(25年-10月-03日)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -39316,7 +39316,7 @@
           <t>B | 579呎 (2房)
 $1696万
 $29,299/呎
-(25年-09月-10日)</t>
+(25年-09月-11日)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -39324,7 +39324,7 @@
           <t>C | 569呎 (3房)
 $1699万
 $29,866/呎
-(25年-11月-17日)</t>
+(25年-11月-18日)</t>
         </is>
       </c>
       <c r="E25" s="21" t="inlineStr">
@@ -39372,7 +39372,7 @@
           <t>J | 549呎 (2房)
 $1635万
 $29,783/呎
-(26年-03月-17日)</t>
+(26年-03月-18日)</t>
         </is>
       </c>
     </row>
@@ -39387,7 +39387,7 @@
           <t>A | 670呎 (3房)
 $2048万
 $30,564/呎
-(25年-10月-27日)</t>
+(25年-10月-28日)</t>
         </is>
       </c>
       <c r="C26" s="22" t="inlineStr">
@@ -39395,7 +39395,7 @@
           <t>B | 579呎 (2房)
 $1688万
 $29,152/呎
-(25年-10月-30日)</t>
+(25年-10月-31日)</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -39403,7 +39403,7 @@
           <t>C | 569呎 (3房)
 $1729万
 $30,392/呎
-(26年-01月-11日)</t>
+(26年-01月-12日)</t>
         </is>
       </c>
       <c r="E26" s="21" t="inlineStr">
@@ -39451,7 +39451,7 @@
           <t>J | 549呎 (2房)
 $1611万
 $29,341/呎
-(26年-03月-19日)</t>
+(26年-03月-20日)</t>
         </is>
       </c>
     </row>
@@ -39466,7 +39466,7 @@
           <t>A | 669呎 (3房)
 $1978万
 $29,568/呎
-(25年-09月-22日)</t>
+(25年-09月-23日)</t>
         </is>
       </c>
       <c r="C27" s="22" t="inlineStr">
@@ -39474,7 +39474,7 @@
           <t>B | 579呎 (2房)
 $1680万
 $29,007/呎
-(25年-10月-22日)</t>
+(25年-10月-23日)</t>
         </is>
       </c>
       <c r="D27" s="22" t="inlineStr">
@@ -39482,7 +39482,7 @@
           <t>C | 568呎 (3房)
 $1682万
 $29,620/呎
-(26年-01月-11日)</t>
+(26年-01月-12日)</t>
         </is>
       </c>
       <c r="E27" s="21" t="inlineStr">
@@ -39530,7 +39530,7 @@
           <t>J | 549呎 (2房)
 $1603万
 $29,195/呎
-(26年-02月-26日)</t>
+(26年-02月-27日)</t>
         </is>
       </c>
     </row>
@@ -39545,7 +39545,7 @@
           <t>A | 669呎 (3房)
 $1968万
 $29,420/呎
-(25年-09月-25日)</t>
+(25年-09月-26日)</t>
         </is>
       </c>
       <c r="C28" s="22" t="inlineStr">
@@ -39553,7 +39553,7 @@
           <t>B | 579呎 (2房)
 $1671万
 $28,862/呎
-(25年-10月-22日)</t>
+(25年-10月-23日)</t>
         </is>
       </c>
       <c r="D28" s="22" t="inlineStr">
@@ -39561,7 +39561,7 @@
           <t>C | 568呎 (3房)
 $1674万
 $29,472/呎
-(25年-10月-23日)</t>
+(25年-10月-24日)</t>
         </is>
       </c>
       <c r="E28" s="21" t="inlineStr">
@@ -39609,7 +39609,7 @@
           <t>J | 549呎 (2房)
 $1611万
 $29,339/呎
-(26年-03月-22日)</t>
+(26年-03月-23日)</t>
         </is>
       </c>
     </row>
@@ -39624,7 +39624,7 @@
           <t>A | 669呎 (3房)
 $1958万
 $29,269/呎
-(25年-10月-02日)</t>
+(25年-10月-03日)</t>
         </is>
       </c>
       <c r="C29" s="22" t="inlineStr">
@@ -39632,7 +39632,7 @@
           <t>B | 579呎 (2房)
 $1646万
 $28,428/呎
-(25年-11月-30日)</t>
+(25年-12月-01日)</t>
         </is>
       </c>
       <c r="D29" s="22" t="inlineStr">
@@ -39640,7 +39640,7 @@
           <t>C | 568呎 (3房)
 $1649万
 $29,030/呎
-(25年-12月-02日)</t>
+(25年-12月-03日)</t>
         </is>
       </c>
       <c r="E29" s="21" t="inlineStr">
@@ -39688,7 +39688,7 @@
           <t>J | 549呎 (2房)
 $1571万
 $28,612/呎
-(26年-02月-26日)</t>
+(26年-02月-27日)</t>
         </is>
       </c>
     </row>
@@ -39703,7 +39703,7 @@
           <t>A | 670呎 (3房)
 $1941万
 $28,972/呎
-(25年-10月-02日)</t>
+(25年-10月-03日)</t>
         </is>
       </c>
       <c r="C30" s="22" t="inlineStr">
@@ -39711,7 +39711,7 @@
           <t>B | 579呎 (2房)
 $1630万
 $28,145/呎
-(25年-10月-12日)</t>
+(25年-10月-13日)</t>
         </is>
       </c>
       <c r="D30" s="22" t="inlineStr">
@@ -39719,7 +39719,7 @@
           <t>C | 568呎 (3房)
 $1632万
 $28,739/呎
-(25年-09月-17日)</t>
+(25年-09月-18日)</t>
         </is>
       </c>
       <c r="E30" s="21" t="inlineStr">
@@ -39767,7 +39767,7 @@
           <t>J | 549呎 (2房)
 $1573万
 $28,648/呎
-(26年-03月-01日)</t>
+(26年-03月-02日)</t>
         </is>
       </c>
     </row>
@@ -39782,7 +39782,7 @@
           <t>A | 670呎 (3房)
 $1902万
 $28,385/呎
-(25年-10月-21日)</t>
+(25年-10月-22日)</t>
         </is>
       </c>
       <c r="C31" s="22" t="inlineStr">
@@ -39790,7 +39790,7 @@
           <t>B | 579呎 (2房)
 $1650万
 $28,496/呎
-(25年-12月-07日)</t>
+(25年-12月-08日)</t>
         </is>
       </c>
       <c r="D31" s="22" t="inlineStr">
@@ -39798,7 +39798,7 @@
           <t>C | 568呎 (3房)
 $1617万
 $28,468/呎
-(25年-12月-09日)</t>
+(25年-12月-10日)</t>
         </is>
       </c>
       <c r="E31" s="21" t="inlineStr">
@@ -39839,7 +39839,7 @@
           <t>J | 549呎 (2房)
 $1555万
 $28,324/呎
-(26年-03月-12日)</t>
+(26年-03月-13日)</t>
         </is>
       </c>
     </row>
@@ -39854,7 +39854,7 @@
           <t>A | 639呎 (2房)
 $1788万
 $27,977/呎
-(25年-11月-04日)</t>
+(25年-11月-05日)</t>
         </is>
       </c>
       <c r="C32" s="24" t="inlineStr"/>
@@ -39883,7 +39883,7 @@
           <t>J | 549呎 (2房)
 $1516万
 $27,623/呎
-(26年-02月-11日)</t>
+(26年-02月-12日)</t>
         </is>
       </c>
     </row>
@@ -39898,7 +39898,7 @@
           <t>A | 639呎 (2房)
 $1761万
 $27,557/呎
-(25年-10月-01日)</t>
+(25年-10月-02日)</t>
         </is>
       </c>
       <c r="C33" s="24" t="inlineStr"/>
@@ -39927,7 +39927,7 @@
           <t>J | 549呎 (2房)
 $1494万
 $27,208/呎
-(26年-03月-01日)</t>
+(26年-03月-02日)</t>
         </is>
       </c>
     </row>

--- a/九龙-启德-维港．湾畔第1B期/维港．湾畔第1B期_销控明细表.xlsx
+++ b/九龙-启德-维港．湾畔第1B期/维港．湾畔第1B期_销控明细表.xlsx
@@ -2572,38 +2572,30 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I29" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>23706000</v>
+      </c>
+      <c r="I29" s="5" t="n">
+        <v>42332</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K29" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L29" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K29" s="5" t="n">
+        <v>23706000</v>
+      </c>
+      <c r="L29" s="5" t="n">
+        <v>42332</v>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
@@ -2612,7 +2604,7 @@
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -4484,7 +4476,7 @@
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr">
@@ -4494,12 +4486,12 @@
       </c>
       <c r="H57" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I57" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J57" s="3" t="inlineStr">
@@ -4509,12 +4501,12 @@
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L57" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M57" s="3" t="inlineStr">
@@ -4524,7 +4516,7 @@
       </c>
       <c r="N57" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -6940,7 +6932,7 @@
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G93" s="3" t="inlineStr">
@@ -6950,12 +6942,12 @@
       </c>
       <c r="H93" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I93" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J93" s="3" t="inlineStr">
@@ -6965,12 +6957,12 @@
       </c>
       <c r="K93" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L93" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M93" s="3" t="inlineStr">
@@ -6980,7 +6972,7 @@
       </c>
       <c r="N93" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -7554,38 +7546,30 @@
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H102" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I102" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="H102" s="5" t="n">
+        <v>18411000</v>
+      </c>
+      <c r="I102" s="5" t="n">
+        <v>32936</v>
       </c>
       <c r="J102" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K102" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L102" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K102" s="5" t="n">
+        <v>18411000</v>
+      </c>
+      <c r="L102" s="5" t="n">
+        <v>32936</v>
       </c>
       <c r="M102" s="3" t="inlineStr">
         <is>
@@ -7594,7 +7578,7 @@
       </c>
       <c r="N102" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -23302,31 +23286,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H336" s="5" t="n">
-        <v>19633000</v>
-      </c>
-      <c r="I336" s="5" t="n">
-        <v>35761</v>
+      <c r="H336" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I336" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J336" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
-        </is>
-      </c>
-      <c r="K336" s="5" t="n">
-        <v>17277040</v>
-      </c>
-      <c r="L336" s="5" t="n">
-        <v>31470</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K336" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L336" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M336" s="3" t="inlineStr">
         <is>
-          <t>120天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N336" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -35197,27 +35189,27 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>187</t>
         </is>
       </c>
     </row>
@@ -35437,12 +35429,12 @@
           <t>32</t>
         </is>
       </c>
-      <c r="B7" s="20" t="inlineStr">
+      <c r="B7" s="22" t="inlineStr">
         <is>
           <t>A | 560呎 (2房)
-招标单位
--
-(在售)</t>
+$2371万
+$42,332/呎
+(26年-07月-31日)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -35817,12 +35809,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="J11" s="21" t="inlineStr">
+      <c r="J11" s="23" t="inlineStr">
         <is>
           <t>J | 559呎 (2房)
--
--
-(待售)</t>
+招标单位
+-
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -36133,12 +36125,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="J15" s="21" t="inlineStr">
+      <c r="J15" s="23" t="inlineStr">
         <is>
           <t>J | 559呎 (2房)
--
--
-(待售)</t>
+招标单位
+-
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -36212,12 +36204,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="J16" s="20" t="inlineStr">
+      <c r="J16" s="22" t="inlineStr">
         <is>
           <t>J | 559呎 (2房)
-招标单位
--
-(在售)</t>
+$1841万
+$32,936/呎
+(26年-07月-31日)</t>
         </is>
       </c>
     </row>
@@ -38422,8 +38414,8 @@
       <c r="J13" s="23" t="inlineStr">
         <is>
           <t>J | 549呎 (2房)
-$1963万
-$35,761/呎
+招标单位
+-
 (已定价未售)</t>
         </is>
       </c>

--- a/九龙-启德-维港．湾畔第1B期/维港．湾畔第1B期_销控明细表.xlsx
+++ b/九龙-启德-维港．湾畔第1B期/维港．湾畔第1B期_销控明细表.xlsx
@@ -3248,7 +3248,7 @@
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
@@ -3258,12 +3258,12 @@
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
@@ -3273,12 +3273,12 @@
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
@@ -3288,7 +3288,7 @@
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -4476,38 +4476,30 @@
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H57" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I57" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="H57" s="5" t="n">
+        <v>18970000</v>
+      </c>
+      <c r="I57" s="5" t="n">
+        <v>33936</v>
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K57" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L57" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K57" s="5" t="n">
+        <v>18970000</v>
+      </c>
+      <c r="L57" s="5" t="n">
+        <v>33936</v>
       </c>
       <c r="M57" s="3" t="inlineStr">
         <is>
@@ -4516,7 +4508,7 @@
       </c>
       <c r="N57" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -5090,7 +5082,7 @@
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G66" s="3" t="inlineStr">
@@ -5100,12 +5092,12 @@
       </c>
       <c r="H66" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I66" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J66" s="3" t="inlineStr">
@@ -5115,12 +5107,12 @@
       </c>
       <c r="K66" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L66" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M66" s="3" t="inlineStr">
@@ -5130,7 +5122,7 @@
       </c>
       <c r="N66" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -6932,7 +6924,7 @@
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G93" s="3" t="inlineStr">
@@ -19084,7 +19076,7 @@
       </c>
       <c r="F273" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G273" s="3" t="inlineStr">
@@ -19092,31 +19084,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H273" s="5" t="n">
-        <v>20946000</v>
-      </c>
-      <c r="I273" s="5" t="n">
-        <v>38153</v>
+      <c r="H273" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I273" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J273" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
-        </is>
-      </c>
-      <c r="K273" s="5" t="n">
-        <v>18432480</v>
-      </c>
-      <c r="L273" s="5" t="n">
-        <v>33575</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K273" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L273" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M273" s="3" t="inlineStr">
         <is>
-          <t>120天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N273" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -21484,7 +21484,7 @@
       </c>
       <c r="F309" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G309" s="3" t="inlineStr">
@@ -21492,31 +21492,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H309" s="5" t="n">
-        <v>20129000</v>
-      </c>
-      <c r="I309" s="5" t="n">
-        <v>36665</v>
+      <c r="H309" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I309" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J309" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
-        </is>
-      </c>
-      <c r="K309" s="5" t="n">
-        <v>17713520</v>
-      </c>
-      <c r="L309" s="5" t="n">
-        <v>32265</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K309" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L309" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M309" s="3" t="inlineStr">
         <is>
-          <t>120天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N309" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -23278,38 +23286,30 @@
       </c>
       <c r="F336" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G336" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H336" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I336" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="H336" s="5" t="n">
+        <v>18487000</v>
+      </c>
+      <c r="I336" s="5" t="n">
+        <v>33674</v>
       </c>
       <c r="J336" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K336" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L336" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K336" s="5" t="n">
+        <v>18487000</v>
+      </c>
+      <c r="L336" s="5" t="n">
+        <v>33674</v>
       </c>
       <c r="M336" s="3" t="inlineStr">
         <is>
@@ -23318,7 +23318,7 @@
       </c>
       <c r="N336" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -35189,17 +35189,17 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>72</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -35209,7 +35209,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>185</t>
         </is>
       </c>
     </row>
@@ -35651,12 +35651,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="J9" s="21" t="inlineStr">
+      <c r="J9" s="20" t="inlineStr">
         <is>
           <t>J | 559呎 (2房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
     </row>
@@ -35809,12 +35809,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="J11" s="23" t="inlineStr">
+      <c r="J11" s="22" t="inlineStr">
         <is>
           <t>J | 559呎 (2房)
-招标单位
--
-(已定价未售)</t>
+$1897万
+$33,936/呎
+(26年-08月-07日)</t>
         </is>
       </c>
     </row>
@@ -35888,12 +35888,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="J12" s="21" t="inlineStr">
+      <c r="J12" s="20" t="inlineStr">
         <is>
           <t>J | 559呎 (2房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
     </row>
@@ -36125,12 +36125,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="J15" s="23" t="inlineStr">
+      <c r="J15" s="20" t="inlineStr">
         <is>
           <t>J | 559呎 (2房)
 招标单位
 -
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -37633,17 +37633,17 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>103</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -37858,12 +37858,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="J6" s="23" t="inlineStr">
+      <c r="J6" s="20" t="inlineStr">
         <is>
           <t>J | 549呎 (2房)
-$2095万
-$38,153/呎
-(已定价未售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
     </row>
@@ -38174,12 +38174,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="J10" s="23" t="inlineStr">
+      <c r="J10" s="20" t="inlineStr">
         <is>
           <t>J | 549呎 (2房)
-$2013万
-$36,665/呎
-(已定价未售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
     </row>
@@ -38411,12 +38411,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="J13" s="23" t="inlineStr">
+      <c r="J13" s="22" t="inlineStr">
         <is>
           <t>J | 549呎 (2房)
-招标单位
--
-(已定价未售)</t>
+$1849万
+$33,674/呎
+(26年-08月-04日)</t>
         </is>
       </c>
     </row>

--- a/九龙-启德-维港．湾畔第1B期/维港．湾畔第1B期_销控明细表.xlsx
+++ b/九龙-启德-维港．湾畔第1B期/维港．湾畔第1B期_销控明细表.xlsx
@@ -2577,7 +2577,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -35434,7 +35434,7 @@
           <t>A | 560呎 (2房)
 $2371万
 $42,332/呎
-(26年-07月-31日)</t>
+(26年-08月-20日)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">

--- a/九龙-启德-维港．湾畔第1B期/维港．湾畔第1B期_销控明细表.xlsx
+++ b/九龙-启德-维港．湾畔第1B期/维港．湾畔第1B期_销控明细表.xlsx
@@ -4481,7 +4481,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
@@ -35814,7 +35814,7 @@
           <t>J | 559呎 (2房)
 $1897万
 $33,936/呎
-(26年-08月-07日)</t>
+(26年-08月-25日)</t>
         </is>
       </c>
     </row>

--- a/九龙-启德-维港．湾畔第1B期/维港．湾畔第1B期_销控明细表.xlsx
+++ b/九龙-启德-维港．湾畔第1B期/维港．湾畔第1B期_销控明细表.xlsx
@@ -23291,7 +23291,7 @@
       </c>
       <c r="G336" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H336" s="5" t="n">
@@ -38416,7 +38416,7 @@
           <t>J | 549呎 (2房)
 $1849万
 $33,674/呎
-(26年-08月-04日)</t>
+(26年-08月-27日)</t>
         </is>
       </c>
     </row>

--- a/九龙-启德-维港．湾畔第1B期/维港．湾畔第1B期_销控明细表.xlsx
+++ b/九龙-启德-维港．湾畔第1B期/维港．湾畔第1B期_销控明细表.xlsx
@@ -7543,7 +7543,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="H102" s="5" t="n">
@@ -36209,7 +36209,7 @@
           <t>J | 559呎 (2房)
 $1841万
 $32,936/呎
-(26年-07月-31日)</t>
+(26年-08月-28日)</t>
         </is>
       </c>
     </row>
